--- a/Result/profitability/2498.xlsx
+++ b/Result/profitability/2498.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM75"/>
+  <dimension ref="A1:AM76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>17.43</v>
       </c>
       <c r="M2" t="n">
-        <v>2.78875</v>
+        <v>2.88</v>
       </c>
       <c r="N2" t="n">
-        <v>37.7825</v>
+        <v>38.00875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -778,10 +778,10 @@
         <v>12.12</v>
       </c>
       <c r="M3" t="n">
-        <v>4.436249999999999</v>
+        <v>4.5175</v>
       </c>
       <c r="N3" t="n">
-        <v>37.1325</v>
+        <v>37.47375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -897,10 +897,10 @@
         <v>8.76</v>
       </c>
       <c r="M4" t="n">
-        <v>5.65375</v>
+        <v>5.005</v>
       </c>
       <c r="N4" t="n">
-        <v>36.48125</v>
+        <v>37.10875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1016,10 +1016,10 @@
         <v>9.25</v>
       </c>
       <c r="M5" t="n">
-        <v>6.202500000000001</v>
+        <v>6.26875</v>
       </c>
       <c r="N5" t="n">
-        <v>36.11</v>
+        <v>36.88125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1135,10 +1135,10 @@
         <v>10.73</v>
       </c>
       <c r="M6" t="n">
-        <v>7.65125</v>
+        <v>7.125</v>
       </c>
       <c r="N6" t="n">
-        <v>35.31875</v>
+        <v>36.2475</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1262,10 +1262,10 @@
         <v>6.54</v>
       </c>
       <c r="M7" t="n">
-        <v>7.98375</v>
+        <v>8.026249999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>34.745</v>
+        <v>35.76875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1389,10 +1389,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>9.104999999999999</v>
+        <v>9.100000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>34.38875</v>
+        <v>34.505</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9951,6 +9951,133 @@
       </c>
       <c r="AM75" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>614</v>
+      </c>
+      <c r="D76" t="n">
+        <v>352</v>
+      </c>
+      <c r="E76" t="n">
+        <v>262</v>
+      </c>
+      <c r="F76" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-573</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-93.23%</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>313</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-260</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-279</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.5687499999999998</v>
+      </c>
+      <c r="N76" t="n">
+        <v>38.595</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0.1379310344827587</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0.9299999999999997</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.02230215827338133</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>-0.6162790697674418</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>6.170000000000002</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0.1692265496434449</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK76" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
